--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Índice de envejecimiento</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="730">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -139,18 +139,18 @@
     <t xml:space="preserve">Primavera</t>
   </si>
   <si>
+    <t xml:space="preserve">11202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
     <t xml:space="preserve">12303</t>
   </si>
   <si>
     <t xml:space="preserve">Timaukel</t>
   </si>
   <si>
-    <t xml:space="preserve">11202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
     <t xml:space="preserve">12104</t>
   </si>
   <si>
@@ -229,18 +229,18 @@
     <t xml:space="preserve">Las Condes</t>
   </si>
   <si>
+    <t xml:space="preserve">6206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paredones</t>
+  </si>
+  <si>
     <t xml:space="preserve">16204</t>
   </si>
   <si>
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
-    <t xml:space="preserve">6206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paredones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valparaiso</t>
   </si>
   <si>
@@ -262,54 +262,54 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
+    <t xml:space="preserve">16206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ránquil</t>
+  </si>
+  <si>
     <t xml:space="preserve">5602</t>
   </si>
   <si>
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
-    <t xml:space="preserve">16206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ránquil</t>
-  </si>
-  <si>
     <t xml:space="preserve">13120</t>
   </si>
   <si>
     <t xml:space="preserve">Ñuñoa</t>
   </si>
   <si>
+    <t xml:space="preserve">16205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
     <t xml:space="preserve">6205</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
   </si>
   <si>
-    <t xml:space="preserve">16205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portezuelo</t>
-  </si>
-  <si>
     <t xml:space="preserve">5604</t>
   </si>
   <si>
     <t xml:space="preserve">El Quisco</t>
   </si>
   <si>
+    <t xml:space="preserve">16207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treguaco</t>
+  </si>
+  <si>
     <t xml:space="preserve">7107</t>
   </si>
   <si>
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
-    <t xml:space="preserve">16207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treguaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">7302</t>
   </si>
   <si>
@@ -322,16 +322,22 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
+    <t xml:space="preserve">13113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
     <t xml:space="preserve">6202</t>
   </si>
   <si>
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
-    <t xml:space="preserve">13113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
+    <t xml:space="preserve">7309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
     <t xml:space="preserve">5109</t>
@@ -340,12 +346,6 @@
     <t xml:space="preserve">Viña del Mar</t>
   </si>
   <si>
-    <t xml:space="preserve">7309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">16107</t>
   </si>
   <si>
@@ -376,16 +376,22 @@
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
+    <t xml:space="preserve">5803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
     <t xml:space="preserve">13129</t>
   </si>
   <si>
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
-    <t xml:space="preserve">5803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
+    <t xml:space="preserve">7202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
   </si>
   <si>
     <t xml:space="preserve">7106</t>
@@ -394,22 +400,28 @@
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
+    <t xml:space="preserve">5101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coelemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">16106</t>
   </si>
   <si>
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">5101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
+    <t xml:space="preserve">7201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">16201</t>
@@ -418,18 +430,6 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
-    <t xml:space="preserve">16203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
     <t xml:space="preserve">16108</t>
   </si>
   <si>
@@ -448,6 +448,12 @@
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
+    <t xml:space="preserve">13110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
     <t xml:space="preserve">7303</t>
   </si>
   <si>
@@ -460,34 +466,64 @@
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
-    <t xml:space="preserve">13110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
     <t xml:space="preserve">5403</t>
   </si>
   <si>
     <t xml:space="preserve">Papudo</t>
   </si>
   <si>
+    <t xml:space="preserve">6307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peralillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
     <t xml:space="preserve">13109</t>
   </si>
   <si>
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
-    <t xml:space="preserve">5603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartagena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peralillo</t>
+    <t xml:space="preserve">6103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
     <t xml:space="preserve">6109</t>
@@ -496,40 +532,10 @@
     <t xml:space="preserve">Malloa</t>
   </si>
   <si>
-    <t xml:space="preserve">6103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coinco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fabián</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
+    <t xml:space="preserve">5606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
   </si>
   <si>
     <t xml:space="preserve">6203</t>
@@ -550,22 +556,28 @@
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
+    <t xml:space="preserve">16104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
     <t xml:space="preserve">5501</t>
   </si>
   <si>
     <t xml:space="preserve">Quillota</t>
   </si>
   <si>
-    <t xml:space="preserve">5606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Carmen</t>
+    <t xml:space="preserve">16301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Carlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peumo</t>
   </si>
   <si>
     <t xml:space="preserve">13117</t>
@@ -574,10 +586,10 @@
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
-    <t xml:space="preserve">16301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Carlos</t>
+    <t xml:space="preserve">6117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
   </si>
   <si>
     <t xml:space="preserve">13203</t>
@@ -592,34 +604,34 @@
     <t xml:space="preserve">San Ramón</t>
   </si>
   <si>
+    <t xml:space="preserve">7307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">13104</t>
   </si>
   <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
-    <t xml:space="preserve">6112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
+    <t xml:space="preserve">7404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
   </si>
   <si>
     <t xml:space="preserve">16109</t>
@@ -628,16 +640,28 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">7404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
+    <t xml:space="preserve">7405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placilla</t>
   </si>
   <si>
     <t xml:space="preserve">16102</t>
@@ -646,28 +670,16 @@
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
-    <t xml:space="preserve">5401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alemana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retiro</t>
+    <t xml:space="preserve">5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
   </si>
   <si>
     <t xml:space="preserve">13126</t>
@@ -676,34 +688,34 @@
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">13111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
     <t xml:space="preserve">5601</t>
   </si>
   <si>
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
+    <t xml:space="preserve">6114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
+  </si>
+  <si>
     <t xml:space="preserve">7110</t>
   </si>
   <si>
     <t xml:space="preserve">San Rafael</t>
   </si>
   <si>
-    <t xml:space="preserve">6114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta de Tilcoco</t>
+    <t xml:space="preserve">7108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longaví</t>
   </si>
   <si>
     <t xml:space="preserve">13130</t>
@@ -712,18 +724,6 @@
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
-    <t xml:space="preserve">7108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">7305</t>
   </si>
   <si>
@@ -736,34 +736,58 @@
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
+    <t xml:space="preserve">5704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
     <t xml:space="preserve">6201</t>
   </si>
   <si>
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
+    <t xml:space="preserve">5301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chépica</t>
+  </si>
+  <si>
     <t xml:space="preserve">13116</t>
   </si>
   <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
-    <t xml:space="preserve">5502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chépica</t>
+    <t xml:space="preserve">6310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
   </si>
   <si>
     <t xml:space="preserve">13127</t>
@@ -772,34 +796,16 @@
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
-    <t xml:space="preserve">5704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">7406</t>
   </si>
   <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">7308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
+    <t xml:space="preserve">7101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talca</t>
   </si>
   <si>
     <t xml:space="preserve">13202</t>
@@ -808,10 +814,10 @@
     <t xml:space="preserve">Pirque</t>
   </si>
   <si>
-    <t xml:space="preserve">7101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
+    <t xml:space="preserve">5402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
   </si>
   <si>
     <t xml:space="preserve">13105</t>
@@ -820,22 +826,28 @@
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
+    <t xml:space="preserve">5503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
     <t xml:space="preserve">5105</t>
   </si>
   <si>
     <t xml:space="preserve">Puchuncaví</t>
   </si>
   <si>
-    <t xml:space="preserve">5503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
+    <t xml:space="preserve">7104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
   </si>
   <si>
     <t xml:space="preserve">13504</t>
@@ -844,16 +856,22 @@
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">7104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
+    <t xml:space="preserve">13505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chillán</t>
   </si>
   <si>
     <t xml:space="preserve">6104</t>
@@ -868,70 +886,58 @@
     <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
-    <t xml:space="preserve">16101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chillán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
     <t xml:space="preserve">7306</t>
   </si>
   <si>
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
+    <t xml:space="preserve">13103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nancagua</t>
+  </si>
+  <si>
     <t xml:space="preserve">13106</t>
   </si>
   <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">13103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codegua</t>
-  </si>
-  <si>
     <t xml:space="preserve">7402</t>
   </si>
   <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
-    <t xml:space="preserve">6107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Cabras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nancagua</t>
+    <t xml:space="preserve">13119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
   </si>
   <si>
     <t xml:space="preserve">5706</t>
@@ -940,10 +946,10 @@
     <t xml:space="preserve">Santa María</t>
   </si>
   <si>
-    <t xml:space="preserve">13119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
+    <t xml:space="preserve">6301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
   </si>
   <si>
     <t xml:space="preserve">7109</t>
@@ -952,52 +958,58 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
-    <t xml:space="preserve">6301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fernando</t>
-  </si>
-  <si>
     <t xml:space="preserve">6303</t>
   </si>
   <si>
     <t xml:space="preserve">Chimbarongo</t>
   </si>
   <si>
+    <t xml:space="preserve">13503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
     <t xml:space="preserve">13101</t>
   </si>
   <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">13503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llaillay</t>
+    <t xml:space="preserve">7408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
     <t xml:space="preserve">6115</t>
@@ -1006,36 +1018,24 @@
     <t xml:space="preserve">Rengo</t>
   </si>
   <si>
-    <t xml:space="preserve">13122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
     <t xml:space="preserve">6101</t>
   </si>
   <si>
     <t xml:space="preserve">Rancagua</t>
   </si>
   <si>
+    <t xml:space="preserve">13501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">13108</t>
   </si>
   <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
-    <t xml:space="preserve">13501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">7301</t>
   </si>
   <si>
@@ -1048,18 +1048,18 @@
     <t xml:space="preserve">Doñihue</t>
   </si>
   <si>
+    <t xml:space="preserve">5303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
     <t xml:space="preserve">16302</t>
   </si>
   <si>
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">5303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
     <t xml:space="preserve">7102</t>
   </si>
   <si>
@@ -1096,30 +1096,30 @@
     <t xml:space="preserve">Requínoa</t>
   </si>
   <si>
+    <t xml:space="preserve">13605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
     <t xml:space="preserve">13303</t>
   </si>
   <si>
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
-    <t xml:space="preserve">13605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
     <t xml:space="preserve">13602</t>
   </si>
   <si>
@@ -1150,18 +1150,18 @@
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
+    <t xml:space="preserve">6106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graneros</t>
+  </si>
+  <si>
     <t xml:space="preserve">13112</t>
   </si>
   <si>
     <t xml:space="preserve">La Pintana</t>
   </si>
   <si>
-    <t xml:space="preserve">6106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graneros</t>
-  </si>
-  <si>
     <t xml:space="preserve">5302</t>
   </si>
   <si>
@@ -1240,6 +1240,12 @@
     <t xml:space="preserve">Macrozona Norte</t>
   </si>
   <si>
+    <t xml:space="preserve">4302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combarbalá</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arica y Parinacota</t>
   </si>
   <si>
@@ -1249,12 +1255,6 @@
     <t xml:space="preserve">Camarones</t>
   </si>
   <si>
-    <t xml:space="preserve">4302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combarbalá</t>
-  </si>
-  <si>
     <t xml:space="preserve">4202</t>
   </si>
   <si>
@@ -1306,18 +1306,18 @@
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
+    <t xml:space="preserve">3304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
     <t xml:space="preserve">4103</t>
   </si>
   <si>
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
-    <t xml:space="preserve">3304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
-  </si>
-  <si>
     <t xml:space="preserve">4301</t>
   </si>
   <si>
@@ -1330,18 +1330,18 @@
     <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
+    <t xml:space="preserve">4101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Serena</t>
+  </si>
+  <si>
     <t xml:space="preserve">3301</t>
   </si>
   <si>
     <t xml:space="preserve">Vallenar</t>
   </si>
   <si>
-    <t xml:space="preserve">4101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Serena</t>
-  </si>
-  <si>
     <t xml:space="preserve">3303</t>
   </si>
   <si>
@@ -1387,18 +1387,18 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">2104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
     <t xml:space="preserve">2301</t>
   </si>
   <si>
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
-    <t xml:space="preserve">2104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
     <t xml:space="preserve">1101</t>
   </si>
   <si>
@@ -1516,40 +1516,46 @@
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
+    <t xml:space="preserve">10306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
     <t xml:space="preserve">10307</t>
   </si>
   <si>
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
-    <t xml:space="preserve">10306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Juan de la Costa</t>
-  </si>
-  <si>
     <t xml:space="preserve">8313</t>
   </si>
   <si>
     <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
+    <t xml:space="preserve">8310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
     <t xml:space="preserve">8104</t>
   </si>
   <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">8309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
+    <t xml:space="preserve">10103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
   </si>
   <si>
     <t xml:space="preserve">8101</t>
@@ -1558,12 +1564,6 @@
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">10103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochamó</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Araucania</t>
   </si>
   <si>
@@ -1585,30 +1585,30 @@
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
+    <t xml:space="preserve">8302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">8106</t>
   </si>
   <si>
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
+    <t xml:space="preserve">8111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
     <t xml:space="preserve">10304</t>
   </si>
   <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
-    <t xml:space="preserve">8111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">9203</t>
   </si>
   <si>
@@ -1627,6 +1627,12 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
+    <t xml:space="preserve">10303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
     <t xml:space="preserve">10104</t>
   </si>
   <si>
@@ -1639,18 +1645,18 @@
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">10303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
     <t xml:space="preserve">9103</t>
   </si>
   <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
+    <t xml:space="preserve">9118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Rios</t>
   </si>
   <si>
@@ -1666,18 +1672,24 @@
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">9118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
     <t xml:space="preserve">14102</t>
   </si>
   <si>
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
+    <t xml:space="preserve">10209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
     <t xml:space="preserve">8112</t>
   </si>
   <si>
@@ -1690,16 +1702,16 @@
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
-    <t xml:space="preserve">10209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
+    <t xml:space="preserve">10210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
     <t xml:space="preserve">8204</t>
@@ -1708,12 +1720,6 @@
     <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
-    <t xml:space="preserve">9210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiguén</t>
-  </si>
-  <si>
     <t xml:space="preserve">9105</t>
   </si>
   <si>
@@ -1738,28 +1744,28 @@
     <t xml:space="preserve">Melipeuco</t>
   </si>
   <si>
-    <t xml:space="preserve">10210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
     <t xml:space="preserve">8304</t>
   </si>
   <si>
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
+    <t xml:space="preserve">14105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máfil</t>
+  </si>
+  <si>
     <t xml:space="preserve">9109</t>
   </si>
   <si>
     <t xml:space="preserve">Loncoche</t>
   </si>
   <si>
-    <t xml:space="preserve">14105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máfil</t>
+    <t xml:space="preserve">10401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
     <t xml:space="preserve">8103</t>
@@ -1780,10 +1786,16 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">10401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaitén</t>
+    <t xml:space="preserve">10106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
   </si>
   <si>
     <t xml:space="preserve">8107</t>
@@ -1792,16 +1804,10 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">10202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Muermos</t>
+    <t xml:space="preserve">8205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
     <t xml:space="preserve">9114</t>
@@ -1810,10 +1816,10 @@
     <t xml:space="preserve">Pitrufquén</t>
   </si>
   <si>
-    <t xml:space="preserve">8205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
+    <t xml:space="preserve">8311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
     <t xml:space="preserve">9207</t>
@@ -1822,12 +1828,6 @@
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
-    <t xml:space="preserve">8311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
     <t xml:space="preserve">8109</t>
   </si>
   <si>
@@ -1852,18 +1852,18 @@
     <t xml:space="preserve">Paillaco</t>
   </si>
   <si>
+    <t xml:space="preserve">9208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
     <t xml:space="preserve">14101</t>
   </si>
   <si>
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
-    <t xml:space="preserve">9208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purén</t>
-  </si>
-  <si>
     <t xml:space="preserve">9116</t>
   </si>
   <si>
@@ -1876,6 +1876,12 @@
     <t xml:space="preserve">Queilén</t>
   </si>
   <si>
+    <t xml:space="preserve">8307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
     <t xml:space="preserve">14203</t>
   </si>
   <si>
@@ -1888,12 +1894,6 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">8307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
     <t xml:space="preserve">10107</t>
   </si>
   <si>
@@ -1906,33 +1906,33 @@
     <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
+    <t xml:space="preserve">14103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
     <t xml:space="preserve">9201</t>
   </si>
   <si>
     <t xml:space="preserve">Angol</t>
   </si>
   <si>
-    <t xml:space="preserve">14103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">10301</t>
   </si>
   <si>
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
+    <t xml:space="preserve">8303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
     <t xml:space="preserve">14104</t>
   </si>
   <si>
-    <t xml:space="preserve">8303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
-  </si>
-  <si>
     <t xml:space="preserve">10102</t>
   </si>
   <si>
@@ -1951,16 +1951,22 @@
     <t xml:space="preserve">Chonchi</t>
   </si>
   <si>
+    <t xml:space="preserve">8201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
     <t xml:space="preserve">9209</t>
   </si>
   <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
-    <t xml:space="preserve">8201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
+    <t xml:space="preserve">14108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
   </si>
   <si>
     <t xml:space="preserve">9113</t>
@@ -1969,12 +1975,6 @@
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
-    <t xml:space="preserve">14108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">9202</t>
   </si>
   <si>
@@ -2029,18 +2029,18 @@
     <t xml:space="preserve">Lautaro</t>
   </si>
   <si>
+    <t xml:space="preserve">9205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonquimay</t>
+  </si>
+  <si>
     <t xml:space="preserve">14202</t>
   </si>
   <si>
     <t xml:space="preserve">Futrono</t>
   </si>
   <si>
-    <t xml:space="preserve">9205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonquimay</t>
-  </si>
-  <si>
     <t xml:space="preserve">9119</t>
   </si>
   <si>
@@ -2077,24 +2077,24 @@
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
+    <t xml:space="preserve">14106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">10109</t>
   </si>
   <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
-    <t xml:space="preserve">14106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">10402</t>
   </si>
   <si>
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:00</t>
+    <t xml:space="preserve">2026-09-04 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2173,16 +2173,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_d_enveje_a_2020.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Indice de envejecimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -2632,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>264.29</v>
+        <v>284.62</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -2664,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>130.21</v>
+        <v>139.51</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
@@ -2696,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>121.23</v>
+        <v>131.11</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>8</v>
@@ -2728,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>114.95</v>
+        <v>123.85</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>8</v>
@@ -2760,7 +2769,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>108.11</v>
+        <v>121.21</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>8</v>
@@ -2792,7 +2801,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>102.85</v>
+        <v>110.46</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>8</v>
@@ -2824,7 +2833,7 @@
         <v>8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>101.89</v>
+        <v>108.8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>8</v>
@@ -2856,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>81.52</v>
+        <v>87.01</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>8</v>
@@ -2888,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>75.82</v>
+        <v>80.38</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>8</v>
@@ -2920,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>71.43</v>
+        <v>76.92</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>8</v>
@@ -2952,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>70.43</v>
+        <v>75.64</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>8</v>
@@ -2984,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>68.39</v>
+        <v>73.74</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>8</v>
@@ -3016,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>64.63</v>
+        <v>68.39</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>8</v>
@@ -3027,10 +3036,10 @@
         <v>2020</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>40</v>
@@ -3048,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>64.29</v>
+        <v>67.13</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>8</v>
@@ -3059,10 +3068,10 @@
         <v>2020</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>42</v>
@@ -3080,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>63.35</v>
+        <v>64.29</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>8</v>
@@ -3112,7 +3121,7 @@
         <v>8</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>56.14</v>
+        <v>62.75</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>8</v>
@@ -3144,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>52.23</v>
+        <v>57.01</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>8</v>
@@ -3176,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>50.98</v>
+        <v>52.7</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>8</v>
@@ -3208,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>38.71</v>
+        <v>40.34</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>8</v>
@@ -3240,7 +3249,7 @@
         <v>8</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.43</v>
+        <v>28.49</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>8</v>
@@ -3272,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>206.82</v>
+        <v>220.45</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>8</v>
@@ -3304,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>191.91</v>
+        <v>207.66</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>8</v>
@@ -3336,7 +3345,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>178.65</v>
+        <v>192.72</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>8</v>
@@ -3368,7 +3377,7 @@
         <v>8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>175.18</v>
+        <v>188.42</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>8</v>
@@ -3400,7 +3409,7 @@
         <v>8</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>169.88</v>
+        <v>184.07</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>8</v>
@@ -3411,10 +3420,10 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>70</v>
@@ -3432,7 +3441,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>168.32</v>
+        <v>183.88</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>8</v>
@@ -3443,10 +3452,10 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>72</v>
@@ -3464,7 +3473,7 @@
         <v>8</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>167.63</v>
+        <v>181.28</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>8</v>
@@ -3496,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>165.64</v>
+        <v>176.75</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>8</v>
@@ -3528,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>161.19</v>
+        <v>174.18</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>8</v>
@@ -3560,7 +3569,7 @@
         <v>8</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>160.84</v>
+        <v>173.99</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>8</v>
@@ -3571,10 +3580,10 @@
         <v>2020</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3592,7 +3601,7 @@
         <v>8</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>159.92</v>
+        <v>172.5</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>8</v>
@@ -3603,10 +3612,10 @@
         <v>2020</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3624,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>157.91</v>
+        <v>170.06</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>8</v>
@@ -3656,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>156.27</v>
+        <v>166.81</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>8</v>
@@ -3667,10 +3676,10 @@
         <v>2020</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3688,7 +3697,7 @@
         <v>8</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>155.45</v>
+        <v>166.71</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>8</v>
@@ -3699,10 +3708,10 @@
         <v>2020</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3720,7 +3729,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>155.05</v>
+        <v>165.65</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>8</v>
@@ -3752,7 +3761,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>152.86</v>
+        <v>164.17</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>8</v>
@@ -3763,10 +3772,10 @@
         <v>2020</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3784,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>152.2</v>
+        <v>164.16</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>8</v>
@@ -3795,10 +3804,10 @@
         <v>2020</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3816,7 +3825,7 @@
         <v>8</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>151.71</v>
+        <v>162.68</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>8</v>
@@ -3848,7 +3857,7 @@
         <v>8</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>148.72</v>
+        <v>158.5</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>8</v>
@@ -3880,7 +3889,7 @@
         <v>8</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>146.08</v>
+        <v>157.78</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>8</v>
@@ -3891,10 +3900,10 @@
         <v>2020</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>101</v>
@@ -3912,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>144.85</v>
+        <v>155.95</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>8</v>
@@ -3923,10 +3932,10 @@
         <v>2020</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3944,7 +3953,7 @@
         <v>8</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>143.01</v>
+        <v>153.55</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>8</v>
@@ -3955,10 +3964,10 @@
         <v>2020</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3976,7 +3985,7 @@
         <v>8</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>139.6</v>
+        <v>152.04</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>8</v>
@@ -3987,10 +3996,10 @@
         <v>2020</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -4008,7 +4017,7 @@
         <v>8</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>138.77</v>
+        <v>150.3</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>8</v>
@@ -4040,7 +4049,7 @@
         <v>8</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>138.14</v>
+        <v>147.62</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>8</v>
@@ -4072,7 +4081,7 @@
         <v>8</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>135.65</v>
+        <v>145.32</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>8</v>
@@ -4104,7 +4113,7 @@
         <v>8</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>134.62</v>
+        <v>144.93</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>8</v>
@@ -4136,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>134.1</v>
+        <v>144.62</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>8</v>
@@ -4168,7 +4177,7 @@
         <v>8</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>133.29</v>
+        <v>142.37</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>8</v>
@@ -4179,10 +4188,10 @@
         <v>2020</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4200,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>131.12</v>
+        <v>140.35</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>8</v>
@@ -4211,10 +4220,10 @@
         <v>2020</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4232,7 +4241,7 @@
         <v>8</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>130.44</v>
+        <v>140.2</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>8</v>
@@ -4264,7 +4273,7 @@
         <v>8</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>128.94</v>
+        <v>138</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>8</v>
@@ -4275,10 +4284,10 @@
         <v>2020</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4296,7 +4305,7 @@
         <v>8</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>128.28</v>
+        <v>137.7</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>8</v>
@@ -4328,7 +4337,7 @@
         <v>8</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>127.36</v>
+        <v>136.91</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>8</v>
@@ -4339,10 +4348,10 @@
         <v>2020</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4360,7 +4369,7 @@
         <v>8</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>127.29</v>
+        <v>136.55</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>8</v>
@@ -4392,7 +4401,7 @@
         <v>8</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>127.18</v>
+        <v>136.52</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>8</v>
@@ -4403,10 +4412,10 @@
         <v>2020</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4424,7 +4433,7 @@
         <v>8</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>127.18</v>
+        <v>136.39</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>8</v>
@@ -4435,10 +4444,10 @@
         <v>2020</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4456,7 +4465,7 @@
         <v>8</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>125.99</v>
+        <v>136.19</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>8</v>
@@ -4488,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>125.78</v>
+        <v>135.73</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>8</v>
@@ -4520,7 +4529,7 @@
         <v>8</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>124.78</v>
+        <v>133</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>8</v>
@@ -4552,7 +4561,7 @@
         <v>8</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>123.54</v>
+        <v>132.92</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>8</v>
@@ -4563,10 +4572,10 @@
         <v>2020</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>143</v>
@@ -4584,7 +4593,7 @@
         <v>8</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>122.95</v>
+        <v>132.13</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>8</v>
@@ -4595,10 +4604,10 @@
         <v>2020</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4616,7 +4625,7 @@
         <v>8</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>122.95</v>
+        <v>131.81</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>8</v>
@@ -4627,10 +4636,10 @@
         <v>2020</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4648,7 +4657,7 @@
         <v>8</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>122.86</v>
+        <v>131.6</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>8</v>
@@ -4680,7 +4689,7 @@
         <v>8</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>121.71</v>
+        <v>131.12</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>8</v>
@@ -4691,10 +4700,10 @@
         <v>2020</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>151</v>
@@ -4712,7 +4721,7 @@
         <v>8</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>120.99</v>
+        <v>130.43</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>8</v>
@@ -4744,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>120.59</v>
+        <v>129.64</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>8</v>
@@ -4755,10 +4764,10 @@
         <v>2020</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4776,7 +4785,7 @@
         <v>8</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>120.54</v>
+        <v>129.52</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>8</v>
@@ -4808,7 +4817,7 @@
         <v>8</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>119.64</v>
+        <v>129.23</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>8</v>
@@ -4819,10 +4828,10 @@
         <v>2020</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>159</v>
@@ -4840,7 +4849,7 @@
         <v>8</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>119.28</v>
+        <v>128.62</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>8</v>
@@ -4851,10 +4860,10 @@
         <v>2020</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4872,7 +4881,7 @@
         <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>119.12</v>
+        <v>128.38</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>8</v>
@@ -4883,10 +4892,10 @@
         <v>2020</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4904,7 +4913,7 @@
         <v>8</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>118.82</v>
+        <v>128.21</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>8</v>
@@ -4915,10 +4924,10 @@
         <v>2020</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4936,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>118.81</v>
+        <v>127.37</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>8</v>
@@ -4947,10 +4956,10 @@
         <v>2020</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4968,7 +4977,7 @@
         <v>8</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>118.69</v>
+        <v>127.26</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>8</v>
@@ -4979,10 +4988,10 @@
         <v>2020</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -5000,7 +5009,7 @@
         <v>8</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>118.05</v>
+        <v>126.55</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>8</v>
@@ -5011,10 +5020,10 @@
         <v>2020</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -5032,7 +5041,7 @@
         <v>8</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>117.44</v>
+        <v>126.01</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>8</v>
@@ -5064,7 +5073,7 @@
         <v>8</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>117.37</v>
+        <v>125.16</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>8</v>
@@ -5075,10 +5084,10 @@
         <v>2020</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5096,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>116.18</v>
+        <v>125.04</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>8</v>
@@ -5128,7 +5137,7 @@
         <v>8</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>115.62</v>
+        <v>124.88</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>8</v>
@@ -5139,10 +5148,10 @@
         <v>2020</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5160,7 +5169,7 @@
         <v>8</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>115.23</v>
+        <v>124.58</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>8</v>
@@ -5171,10 +5180,10 @@
         <v>2020</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5192,7 +5201,7 @@
         <v>8</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>115.05</v>
+        <v>124.46</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>8</v>
@@ -5203,10 +5212,10 @@
         <v>2020</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5224,7 +5233,7 @@
         <v>8</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>114.56</v>
+        <v>122.8</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>8</v>
@@ -5235,10 +5244,10 @@
         <v>2020</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5256,7 +5265,7 @@
         <v>8</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>114.07</v>
+        <v>122.75</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>8</v>
@@ -5288,7 +5297,7 @@
         <v>8</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>113.91</v>
+        <v>122.46</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>8</v>
@@ -5299,10 +5308,10 @@
         <v>2020</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5320,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>113.64</v>
+        <v>122.45</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>8</v>
@@ -5352,7 +5361,7 @@
         <v>8</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>113.54</v>
+        <v>122.38</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>8</v>
@@ -5363,10 +5372,10 @@
         <v>2020</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5384,7 +5393,7 @@
         <v>8</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>113.36</v>
+        <v>121.65</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>8</v>
@@ -5395,10 +5404,10 @@
         <v>2020</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5416,7 +5425,7 @@
         <v>8</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>113.19</v>
+        <v>121.45</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>8</v>
@@ -5427,10 +5436,10 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5448,7 +5457,7 @@
         <v>8</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>112.76</v>
+        <v>121.44</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>8</v>
@@ -5459,10 +5468,10 @@
         <v>2020</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>199</v>
@@ -5480,7 +5489,7 @@
         <v>8</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>112.65</v>
+        <v>121.37</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>8</v>
@@ -5491,10 +5500,10 @@
         <v>2020</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5512,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>112.52</v>
+        <v>121.22</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>8</v>
@@ -5544,7 +5553,7 @@
         <v>8</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>112.5</v>
+        <v>121</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>8</v>
@@ -5576,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>111.81</v>
+        <v>120.58</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>8</v>
@@ -5587,10 +5596,10 @@
         <v>2020</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5608,7 +5617,7 @@
         <v>8</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>111.74</v>
+        <v>119.96</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>8</v>
@@ -5640,7 +5649,7 @@
         <v>8</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>111.43</v>
+        <v>119.73</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>8</v>
@@ -5672,7 +5681,7 @@
         <v>8</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>111.36</v>
+        <v>119.59</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>8</v>
@@ -5704,7 +5713,7 @@
         <v>8</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>110.96</v>
+        <v>119.58</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>8</v>
@@ -5715,10 +5724,10 @@
         <v>2020</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5736,7 +5745,7 @@
         <v>8</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>110.9</v>
+        <v>119.38</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>8</v>
@@ -5747,10 +5756,10 @@
         <v>2020</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5768,7 +5777,7 @@
         <v>8</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>110.34</v>
+        <v>118.07</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>8</v>
@@ -5800,7 +5809,7 @@
         <v>8</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>110.29</v>
+        <v>117.92</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>8</v>
@@ -5811,10 +5820,10 @@
         <v>2020</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5832,7 +5841,7 @@
         <v>8</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>109.67</v>
+        <v>117.57</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>8</v>
@@ -5864,7 +5873,7 @@
         <v>8</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>109.37</v>
+        <v>117.47</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>8</v>
@@ -5875,10 +5884,10 @@
         <v>2020</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>225</v>
@@ -5896,7 +5905,7 @@
         <v>8</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>108.66</v>
+        <v>117.27</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>8</v>
@@ -5907,10 +5916,10 @@
         <v>2020</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5928,7 +5937,7 @@
         <v>8</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>108.47</v>
+        <v>116.91</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>8</v>
@@ -5939,10 +5948,10 @@
         <v>2020</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5960,7 +5969,7 @@
         <v>8</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>108.32</v>
+        <v>116.13</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>8</v>
@@ -5992,7 +6001,7 @@
         <v>8</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>108.01</v>
+        <v>115.68</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>8</v>
@@ -6003,10 +6012,10 @@
         <v>2020</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>233</v>
@@ -6024,7 +6033,7 @@
         <v>8</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>107.02</v>
+        <v>115.23</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>8</v>
@@ -6056,7 +6065,7 @@
         <v>8</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>106.59</v>
+        <v>114.98</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>8</v>
@@ -6088,7 +6097,7 @@
         <v>8</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>106.56</v>
+        <v>114.86</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>8</v>
@@ -6099,10 +6108,10 @@
         <v>2020</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6120,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>106.45</v>
+        <v>114.33</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>8</v>
@@ -6131,10 +6140,10 @@
         <v>2020</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6152,7 +6161,7 @@
         <v>8</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>106.35</v>
+        <v>114.12</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>8</v>
@@ -6184,7 +6193,7 @@
         <v>8</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>106.34</v>
+        <v>114.11</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>8</v>
@@ -6216,7 +6225,7 @@
         <v>8</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>105.88</v>
+        <v>113.94</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>8</v>
@@ -6248,7 +6257,7 @@
         <v>8</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>105.47</v>
+        <v>113.48</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>8</v>
@@ -6280,7 +6289,7 @@
         <v>8</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>104.7</v>
+        <v>113.42</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>8</v>
@@ -6291,10 +6300,10 @@
         <v>2020</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>251</v>
@@ -6312,7 +6321,7 @@
         <v>8</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>104.58</v>
+        <v>112.73</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>8</v>
@@ -6323,10 +6332,10 @@
         <v>2020</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>253</v>
@@ -6344,7 +6353,7 @@
         <v>8</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>104.48</v>
+        <v>111.91</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>8</v>
@@ -6355,10 +6364,10 @@
         <v>2020</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6376,7 +6385,7 @@
         <v>8</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>103.93</v>
+        <v>111.88</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>8</v>
@@ -6387,10 +6396,10 @@
         <v>2020</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6408,7 +6417,7 @@
         <v>8</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>103.91</v>
+        <v>111.83</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>8</v>
@@ -6440,7 +6449,7 @@
         <v>8</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>103.57</v>
+        <v>111.8</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>8</v>
@@ -6451,10 +6460,10 @@
         <v>2020</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6472,7 +6481,7 @@
         <v>8</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>103.04</v>
+        <v>110.23</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>8</v>
@@ -6483,10 +6492,10 @@
         <v>2020</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6504,7 +6513,7 @@
         <v>8</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>102.26</v>
+        <v>109.81</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>8</v>
@@ -6515,10 +6524,10 @@
         <v>2020</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6536,7 +6545,7 @@
         <v>8</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>102.19</v>
+        <v>109.64</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>8</v>
@@ -6547,10 +6556,10 @@
         <v>2020</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6568,7 +6577,7 @@
         <v>8</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>101.89</v>
+        <v>109.28</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>8</v>
@@ -6600,7 +6609,7 @@
         <v>8</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>101.69</v>
+        <v>108.86</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>8</v>
@@ -6632,7 +6641,7 @@
         <v>8</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>101.54</v>
+        <v>108.78</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>8</v>
@@ -6643,10 +6652,10 @@
         <v>2020</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6664,7 +6673,7 @@
         <v>8</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>101.15</v>
+        <v>108.07</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>8</v>
@@ -6696,7 +6705,7 @@
         <v>8</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>100.93</v>
+        <v>107.88</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>8</v>
@@ -6707,10 +6716,10 @@
         <v>2020</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6728,7 +6737,7 @@
         <v>8</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>100.48</v>
+        <v>107.67</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>8</v>
@@ -6739,10 +6748,10 @@
         <v>2020</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6760,7 +6769,7 @@
         <v>8</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>100.45</v>
+        <v>107.5</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>8</v>
@@ -6771,10 +6780,10 @@
         <v>2020</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6792,7 +6801,7 @@
         <v>8</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>99.78</v>
+        <v>107.27</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>8</v>
@@ -6824,7 +6833,7 @@
         <v>8</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>99.59</v>
+        <v>107.22</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>8</v>
@@ -6835,10 +6844,10 @@
         <v>2020</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6856,7 +6865,7 @@
         <v>8</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>99.22</v>
+        <v>107.08</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>8</v>
@@ -6867,10 +6876,10 @@
         <v>2020</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6888,7 +6897,7 @@
         <v>8</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>99.05</v>
+        <v>106.71</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>8</v>
@@ -6899,10 +6908,10 @@
         <v>2020</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6920,7 +6929,7 @@
         <v>8</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>99.04</v>
+        <v>106.44</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>8</v>
@@ -6952,7 +6961,7 @@
         <v>8</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>98.99</v>
+        <v>106</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>8</v>
@@ -6984,7 +6993,7 @@
         <v>8</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>98.83</v>
+        <v>105.91</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>8</v>
@@ -7016,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>98.81</v>
+        <v>105.39</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>8</v>
@@ -7048,7 +7057,7 @@
         <v>8</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>98.51</v>
+        <v>105.1</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>8</v>
@@ -7059,10 +7068,10 @@
         <v>2020</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7080,7 +7089,7 @@
         <v>8</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>97.85</v>
+        <v>104.98</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>8</v>
@@ -7091,10 +7100,10 @@
         <v>2020</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7112,7 +7121,7 @@
         <v>8</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>97.8</v>
+        <v>104.85</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>8</v>
@@ -7123,10 +7132,10 @@
         <v>2020</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7144,7 +7153,7 @@
         <v>8</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>97.64</v>
+        <v>104.82</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>8</v>
@@ -7155,10 +7164,10 @@
         <v>2020</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7176,7 +7185,7 @@
         <v>8</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>96.61</v>
+        <v>103.85</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>8</v>
@@ -7187,10 +7196,10 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7208,7 +7217,7 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>96.39</v>
+        <v>103.14</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>8</v>
@@ -7219,10 +7228,10 @@
         <v>2020</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7240,7 +7249,7 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>95.61</v>
+        <v>102.86</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>8</v>
@@ -7251,10 +7260,10 @@
         <v>2020</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7272,7 +7281,7 @@
         <v>8</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>95.32</v>
+        <v>102.68</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>8</v>
@@ -7304,7 +7313,7 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>94.73</v>
+        <v>101.87</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>8</v>
@@ -7336,7 +7345,7 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>94.01</v>
+        <v>100.66</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>8</v>
@@ -7347,10 +7356,10 @@
         <v>2020</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7368,7 +7377,7 @@
         <v>8</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>94</v>
+        <v>100.4</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>8</v>
@@ -7400,7 +7409,7 @@
         <v>8</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>93.76</v>
+        <v>100.11</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>8</v>
@@ -7432,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>93.69</v>
+        <v>100.08</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>8</v>
@@ -7464,7 +7473,7 @@
         <v>8</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>93.15</v>
+        <v>99.51</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>8</v>
@@ -7475,10 +7484,10 @@
         <v>2020</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7496,7 +7505,7 @@
         <v>8</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>92.9</v>
+        <v>99.09</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>8</v>
@@ -7507,10 +7516,10 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7528,7 +7537,7 @@
         <v>8</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>90.98</v>
+        <v>98.63</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>8</v>
@@ -7560,7 +7569,7 @@
         <v>8</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>90.85</v>
+        <v>98</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>8</v>
@@ -7571,10 +7580,10 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7592,7 +7601,7 @@
         <v>8</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>90.76</v>
+        <v>97.52</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>8</v>
@@ -7624,7 +7633,7 @@
         <v>8</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>90.13</v>
+        <v>96.93</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>8</v>
@@ -7656,7 +7665,7 @@
         <v>8</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>89.63</v>
+        <v>95.55</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>8</v>
@@ -7688,7 +7697,7 @@
         <v>8</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>89.18</v>
+        <v>94.87</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>8</v>
@@ -7720,7 +7729,7 @@
         <v>8</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>88.41</v>
+        <v>94.77</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>8</v>
@@ -7752,7 +7761,7 @@
         <v>8</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>87.65</v>
+        <v>94.45</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>8</v>
@@ -7763,10 +7772,10 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7784,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>87.52</v>
+        <v>93.94</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>8</v>
@@ -7795,10 +7804,10 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7816,7 +7825,7 @@
         <v>8</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>87</v>
+        <v>93.76</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>8</v>
@@ -7848,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>86.15</v>
+        <v>92.25</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>8</v>
@@ -7880,7 +7889,7 @@
         <v>8</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>85.94</v>
+        <v>91.97</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>8</v>
@@ -7912,7 +7921,7 @@
         <v>8</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>85.87</v>
+        <v>91.5</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>8</v>
@@ -7944,7 +7953,7 @@
         <v>8</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>85.07</v>
+        <v>91.43</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>8</v>
@@ -7976,7 +7985,7 @@
         <v>8</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>84.73</v>
+        <v>90.76</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>8</v>
@@ -8008,7 +8017,7 @@
         <v>8</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>82.51</v>
+        <v>88.67</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>8</v>
@@ -8040,7 +8049,7 @@
         <v>8</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>80.65</v>
+        <v>86.79</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>8</v>
@@ -8072,7 +8081,7 @@
         <v>8</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>80.62</v>
+        <v>85.82</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>8</v>
@@ -8104,7 +8113,7 @@
         <v>8</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>80.16</v>
+        <v>85.57</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>8</v>
@@ -8136,7 +8145,7 @@
         <v>8</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>79.48</v>
+        <v>85.47</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>8</v>
@@ -8168,7 +8177,7 @@
         <v>8</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>79.01</v>
+        <v>84.27</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>8</v>
@@ -8200,7 +8209,7 @@
         <v>8</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>77.74</v>
+        <v>83.55</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>8</v>
@@ -8232,7 +8241,7 @@
         <v>8</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>76.95</v>
+        <v>82.59</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>8</v>
@@ -8264,7 +8273,7 @@
         <v>8</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>76.78</v>
+        <v>82.58</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>8</v>
@@ -8296,7 +8305,7 @@
         <v>8</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>76.72</v>
+        <v>82.42</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>8</v>
@@ -8307,10 +8316,10 @@
         <v>2020</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8328,7 +8337,7 @@
         <v>8</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>76</v>
+        <v>81.77</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>8</v>
@@ -8339,10 +8348,10 @@
         <v>2020</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8360,7 +8369,7 @@
         <v>8</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>75.99</v>
+        <v>81.44</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>8</v>
@@ -8392,7 +8401,7 @@
         <v>8</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>75.56</v>
+        <v>80.98</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>8</v>
@@ -8424,7 +8433,7 @@
         <v>8</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>73.48</v>
+        <v>78.61</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>8</v>
@@ -8456,7 +8465,7 @@
         <v>8</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>69.95</v>
+        <v>76.32</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>8</v>
@@ -8488,7 +8497,7 @@
         <v>8</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>67.35</v>
+        <v>72.38</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>8</v>
@@ -8520,7 +8529,7 @@
         <v>8</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>67.35</v>
+        <v>72.02</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>8</v>
@@ -8552,7 +8561,7 @@
         <v>8</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>65.86</v>
+        <v>70.09</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>8</v>
@@ -8584,7 +8593,7 @@
         <v>8</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>61.07</v>
+        <v>65.66</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>8</v>
@@ -8616,7 +8625,7 @@
         <v>8</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>52.64</v>
+        <v>56.67</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>8</v>
@@ -8648,7 +8657,7 @@
         <v>8</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>46.44</v>
+        <v>49.26</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>8</v>
@@ -8680,7 +8689,7 @@
         <v>8</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>44.68</v>
+        <v>47.72</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>8</v>
@@ -8712,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>40.13</v>
+        <v>42.72</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>8</v>
@@ -8744,7 +8753,7 @@
         <v>8</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>161.51</v>
+        <v>177.47</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>8</v>
@@ -8755,16 +8764,16 @@
         <v>2020</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D194" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="E194" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>405</v>
@@ -8776,7 +8785,7 @@
         <v>8</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>144.85</v>
+        <v>154.83</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>8</v>
@@ -8787,10 +8796,10 @@
         <v>2020</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>410</v>
@@ -8808,7 +8817,7 @@
         <v>8</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>143.8</v>
+        <v>154.19</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>8</v>
@@ -8840,7 +8849,7 @@
         <v>8</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>134.72</v>
+        <v>142.91</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>8</v>
@@ -8872,7 +8881,7 @@
         <v>8</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>115.59</v>
+        <v>123.51</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>8</v>
@@ -8904,7 +8913,7 @@
         <v>8</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>106.83</v>
+        <v>115.04</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>8</v>
@@ -8936,7 +8945,7 @@
         <v>8</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>105.87</v>
+        <v>113.61</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>8</v>
@@ -8968,7 +8977,7 @@
         <v>8</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>105.47</v>
+        <v>112.77</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>8</v>
@@ -9000,7 +9009,7 @@
         <v>8</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>101.19</v>
+        <v>108.63</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>8</v>
@@ -9032,7 +9041,7 @@
         <v>8</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>100.02</v>
+        <v>107.19</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>8</v>
@@ -9064,7 +9073,7 @@
         <v>8</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>97.79</v>
+        <v>104.82</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>8</v>
@@ -9075,10 +9084,10 @@
         <v>2020</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>429</v>
@@ -9096,7 +9105,7 @@
         <v>8</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>97.36</v>
+        <v>104.23</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>8</v>
@@ -9107,10 +9116,10 @@
         <v>2020</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>431</v>
@@ -9128,7 +9137,7 @@
         <v>8</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>97.18</v>
+        <v>104.1</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>8</v>
@@ -9160,7 +9169,7 @@
         <v>8</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>93.07</v>
+        <v>100.2</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>8</v>
@@ -9192,7 +9201,7 @@
         <v>8</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>90.29</v>
+        <v>96.56</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>8</v>
@@ -9203,10 +9212,10 @@
         <v>2020</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>437</v>
@@ -9224,7 +9233,7 @@
         <v>8</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>89.4</v>
+        <v>96.34</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>8</v>
@@ -9235,10 +9244,10 @@
         <v>2020</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>439</v>
@@ -9256,7 +9265,7 @@
         <v>8</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>89.19</v>
+        <v>95.74</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>8</v>
@@ -9288,7 +9297,7 @@
         <v>8</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>86.2</v>
+        <v>92.12</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>8</v>
@@ -9320,7 +9329,7 @@
         <v>8</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>84.93</v>
+        <v>90.96</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>8</v>
@@ -9334,7 +9343,7 @@
         <v>15</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>444</v>
@@ -9352,7 +9361,7 @@
         <v>8</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>84.39</v>
+        <v>90.71</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>8</v>
@@ -9384,7 +9393,7 @@
         <v>8</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>84.18</v>
+        <v>89.61</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>8</v>
@@ -9416,7 +9425,7 @@
         <v>8</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>83.56</v>
+        <v>88.83</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>8</v>
@@ -9448,7 +9457,7 @@
         <v>8</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>82.64</v>
+        <v>88.31</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>8</v>
@@ -9462,7 +9471,7 @@
         <v>15</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>453</v>
@@ -9480,7 +9489,7 @@
         <v>8</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>82</v>
+        <v>87.23</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>8</v>
@@ -9512,7 +9521,7 @@
         <v>8</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>79.79</v>
+        <v>86.07</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>8</v>
@@ -9544,7 +9553,7 @@
         <v>8</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>79.77</v>
+        <v>85.25</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>8</v>
@@ -9576,7 +9585,7 @@
         <v>8</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>79.23</v>
+        <v>84.42</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>8</v>
@@ -9608,7 +9617,7 @@
         <v>8</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>77.18</v>
+        <v>81.58</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>8</v>
@@ -9622,7 +9631,7 @@
         <v>15</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9640,7 +9649,7 @@
         <v>8</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>76.09</v>
+        <v>81.15</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>8</v>
@@ -9672,7 +9681,7 @@
         <v>8</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>74.15</v>
+        <v>79.14</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>8</v>
@@ -9704,7 +9713,7 @@
         <v>8</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>71.89</v>
+        <v>76.87</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>8</v>
@@ -9736,7 +9745,7 @@
         <v>8</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>67.05</v>
+        <v>71.69</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>8</v>
@@ -9768,7 +9777,7 @@
         <v>8</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>64.39</v>
+        <v>69.61</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>8</v>
@@ -9800,7 +9809,7 @@
         <v>8</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>63.77</v>
+        <v>67.99</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>8</v>
@@ -9832,7 +9841,7 @@
         <v>8</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>63.4</v>
+        <v>67.4</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>8</v>
@@ -9864,7 +9873,7 @@
         <v>8</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>54.53</v>
+        <v>58.49</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>8</v>
@@ -9896,7 +9905,7 @@
         <v>8</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>53.81</v>
+        <v>57.61</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>8</v>
@@ -9928,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>53.14</v>
+        <v>56.78</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>8</v>
@@ -9960,7 +9969,7 @@
         <v>8</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>49.21</v>
+        <v>52.52</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>8</v>
@@ -9992,7 +10001,7 @@
         <v>8</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>49.02</v>
+        <v>52.08</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>8</v>
@@ -10024,7 +10033,7 @@
         <v>8</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>41.98</v>
+        <v>44.39</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>8</v>
@@ -10056,7 +10065,7 @@
         <v>8</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>32.89</v>
+        <v>34.36</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>8</v>
@@ -10088,7 +10097,7 @@
         <v>8</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>31.61</v>
+        <v>33.72</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>8</v>
@@ -10120,7 +10129,7 @@
         <v>8</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>159.91</v>
+        <v>169.78</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>8</v>
@@ -10152,7 +10161,7 @@
         <v>8</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>154.74</v>
+        <v>165.75</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>8</v>
@@ -10184,7 +10193,7 @@
         <v>8</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>152.4</v>
+        <v>165.28</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>8</v>
@@ -10216,7 +10225,7 @@
         <v>8</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>139.96</v>
+        <v>151.42</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>8</v>
@@ -10248,7 +10257,7 @@
         <v>8</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>136.88</v>
+        <v>150.43</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>8</v>
@@ -10280,7 +10289,7 @@
         <v>8</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>136.36</v>
+        <v>146.85</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>8</v>
@@ -10312,7 +10321,7 @@
         <v>8</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>135.13</v>
+        <v>145.81</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>8</v>
@@ -10323,10 +10332,10 @@
         <v>2020</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>511</v>
@@ -10344,7 +10353,7 @@
         <v>8</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>133.41</v>
+        <v>144.95</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>8</v>
@@ -10355,10 +10364,10 @@
         <v>2020</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>513</v>
@@ -10376,7 +10385,7 @@
         <v>8</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>131.47</v>
+        <v>143.4</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>8</v>
@@ -10408,7 +10417,7 @@
         <v>8</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>131.19</v>
+        <v>141.27</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>8</v>
@@ -10440,7 +10449,7 @@
         <v>8</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>130.04</v>
+        <v>139.98</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>8</v>
@@ -10472,7 +10481,7 @@
         <v>8</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>129.1</v>
+        <v>139.23</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>8</v>
@@ -10504,7 +10513,7 @@
         <v>8</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>127.9</v>
+        <v>139</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>8</v>
@@ -10515,10 +10524,10 @@
         <v>2020</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>524</v>
@@ -10536,7 +10545,7 @@
         <v>8</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>127.9</v>
+        <v>138.41</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>8</v>
@@ -10568,7 +10577,7 @@
         <v>8</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>127.66</v>
+        <v>137.92</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>8</v>
@@ -10579,10 +10588,10 @@
         <v>2020</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>528</v>
@@ -10600,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>127.62</v>
+        <v>137.61</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>8</v>
@@ -10632,7 +10641,7 @@
         <v>8</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>127.15</v>
+        <v>136.79</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>8</v>
@@ -10664,7 +10673,7 @@
         <v>8</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>125.28</v>
+        <v>134.78</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>8</v>
@@ -10696,7 +10705,7 @@
         <v>8</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>124.57</v>
+        <v>134.13</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>8</v>
@@ -10728,7 +10737,7 @@
         <v>8</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>122.33</v>
+        <v>132.15</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>8</v>
@@ -10739,10 +10748,10 @@
         <v>2020</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>538</v>
@@ -10760,7 +10769,7 @@
         <v>8</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>122.09</v>
+        <v>131.98</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>8</v>
@@ -10771,10 +10780,10 @@
         <v>2020</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>540</v>
@@ -10792,7 +10801,7 @@
         <v>8</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>122.09</v>
+        <v>131.97</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>8</v>
@@ -10824,7 +10833,7 @@
         <v>8</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>122.02</v>
+        <v>130.89</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>8</v>
@@ -10835,16 +10844,16 @@
         <v>2020</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D259" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="D259" s="2" t="s">
+      <c r="E259" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>496</v>
@@ -10856,7 +10865,7 @@
         <v>8</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>117.78</v>
+        <v>127.68</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>8</v>
@@ -10867,10 +10876,10 @@
         <v>2020</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>498</v>
+        <v>546</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>547</v>
@@ -10888,7 +10897,7 @@
         <v>8</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>117.53</v>
+        <v>127.53</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>8</v>
@@ -10899,10 +10908,10 @@
         <v>2020</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>549</v>
@@ -10920,7 +10929,7 @@
         <v>8</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>117</v>
+        <v>127.37</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>8</v>
@@ -10934,7 +10943,7 @@
         <v>14</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>551</v>
@@ -10952,7 +10961,7 @@
         <v>8</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>116.6</v>
+        <v>127.15</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>8</v>
@@ -10963,10 +10972,10 @@
         <v>2020</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>553</v>
@@ -10984,7 +10993,7 @@
         <v>8</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>115.71</v>
+        <v>126.02</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>8</v>
@@ -11016,7 +11025,7 @@
         <v>8</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>115.34</v>
+        <v>124.37</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>8</v>
@@ -11027,10 +11036,10 @@
         <v>2020</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>557</v>
@@ -11048,7 +11057,7 @@
         <v>8</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>115.02</v>
+        <v>124.33</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>8</v>
@@ -11080,7 +11089,7 @@
         <v>8</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>114.83</v>
+        <v>124.26</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>8</v>
@@ -11091,10 +11100,10 @@
         <v>2020</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>561</v>
@@ -11112,7 +11121,7 @@
         <v>8</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>114.42</v>
+        <v>123.96</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>8</v>
@@ -11144,7 +11153,7 @@
         <v>8</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>114.31</v>
+        <v>123.74</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>8</v>
@@ -11155,10 +11164,10 @@
         <v>2020</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>565</v>
@@ -11176,7 +11185,7 @@
         <v>8</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>113.91</v>
+        <v>123.73</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>8</v>
@@ -11187,10 +11196,10 @@
         <v>2020</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>567</v>
@@ -11208,7 +11217,7 @@
         <v>8</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>113.85</v>
+        <v>123.09</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>8</v>
@@ -11219,10 +11228,10 @@
         <v>2020</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>569</v>
@@ -11240,7 +11249,7 @@
         <v>8</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>113.75</v>
+        <v>123.08</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>8</v>
@@ -11272,7 +11281,7 @@
         <v>8</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>113.72</v>
+        <v>123.04</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>8</v>
@@ -11283,10 +11292,10 @@
         <v>2020</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>573</v>
@@ -11304,7 +11313,7 @@
         <v>8</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>113.2</v>
+        <v>121.99</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>8</v>
@@ -11336,7 +11345,7 @@
         <v>8</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>111.63</v>
+        <v>120.8</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>8</v>
@@ -11347,10 +11356,10 @@
         <v>2020</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>577</v>
@@ -11368,7 +11377,7 @@
         <v>8</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>111.02</v>
+        <v>120.6</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>8</v>
@@ -11379,10 +11388,10 @@
         <v>2020</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>579</v>
@@ -11400,7 +11409,7 @@
         <v>8</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>110.82</v>
+        <v>120.26</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>8</v>
@@ -11411,10 +11420,10 @@
         <v>2020</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>581</v>
@@ -11432,7 +11441,7 @@
         <v>8</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>110.33</v>
+        <v>119.89</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>8</v>
@@ -11443,10 +11452,10 @@
         <v>2020</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>583</v>
@@ -11464,7 +11473,7 @@
         <v>8</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>110.3</v>
+        <v>119.42</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>8</v>
@@ -11475,10 +11484,10 @@
         <v>2020</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>585</v>
@@ -11496,7 +11505,7 @@
         <v>8</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>109.35</v>
+        <v>118.98</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>8</v>
@@ -11507,10 +11516,10 @@
         <v>2020</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>587</v>
@@ -11528,7 +11537,7 @@
         <v>8</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>109.25</v>
+        <v>118.54</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>8</v>
@@ -11539,10 +11548,10 @@
         <v>2020</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>589</v>
@@ -11560,7 +11569,7 @@
         <v>8</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>109.2</v>
+        <v>118.33</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>8</v>
@@ -11592,7 +11601,7 @@
         <v>8</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>109.01</v>
+        <v>117.66</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>8</v>
@@ -11603,10 +11612,10 @@
         <v>2020</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>593</v>
@@ -11624,7 +11633,7 @@
         <v>8</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>109</v>
+        <v>117.07</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>8</v>
@@ -11635,10 +11644,10 @@
         <v>2020</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>595</v>
@@ -11656,7 +11665,7 @@
         <v>8</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>108.32</v>
+        <v>116.7</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>8</v>
@@ -11667,10 +11676,10 @@
         <v>2020</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>597</v>
@@ -11688,7 +11697,7 @@
         <v>8</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>107.4</v>
+        <v>116.57</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>8</v>
@@ -11699,10 +11708,10 @@
         <v>2020</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>599</v>
@@ -11720,7 +11729,7 @@
         <v>8</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>106.91</v>
+        <v>115.45</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>8</v>
@@ -11731,10 +11740,10 @@
         <v>2020</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>601</v>
@@ -11752,7 +11761,7 @@
         <v>8</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>106.86</v>
+        <v>115.4</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>8</v>
@@ -11784,7 +11793,7 @@
         <v>8</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>106.68</v>
+        <v>114.95</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>8</v>
@@ -11816,7 +11825,7 @@
         <v>8</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>105.51</v>
+        <v>113.93</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>8</v>
@@ -11848,7 +11857,7 @@
         <v>8</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>104.68</v>
+        <v>112.96</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>8</v>
@@ -11862,7 +11871,7 @@
         <v>14</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>609</v>
@@ -11880,7 +11889,7 @@
         <v>8</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>104.45</v>
+        <v>112.76</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>8</v>
@@ -11891,10 +11900,10 @@
         <v>2020</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>611</v>
@@ -11912,7 +11921,7 @@
         <v>8</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>104.32</v>
+        <v>112.73</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>8</v>
@@ -11923,10 +11932,10 @@
         <v>2020</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>613</v>
@@ -11944,7 +11953,7 @@
         <v>8</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>104.31</v>
+        <v>112.08</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>8</v>
@@ -11976,7 +11985,7 @@
         <v>8</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>104.29</v>
+        <v>110.92</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>8</v>
@@ -12008,7 +12017,7 @@
         <v>8</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>102.74</v>
+        <v>110.41</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>8</v>
@@ -12019,10 +12028,10 @@
         <v>2020</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>544</v>
+        <v>493</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>619</v>
@@ -12040,7 +12049,7 @@
         <v>8</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>102.64</v>
+        <v>109.79</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>8</v>
@@ -12051,10 +12060,10 @@
         <v>2020</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>621</v>
@@ -12072,7 +12081,7 @@
         <v>8</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>101.01</v>
+        <v>109.76</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>8</v>
@@ -12104,7 +12113,7 @@
         <v>8</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>100.8</v>
+        <v>109.46</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>8</v>
@@ -12136,7 +12145,7 @@
         <v>8</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>100.24</v>
+        <v>108.54</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>8</v>
@@ -12168,7 +12177,7 @@
         <v>8</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>99.58</v>
+        <v>108.02</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>8</v>
@@ -12179,10 +12188,10 @@
         <v>2020</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>629</v>
@@ -12200,7 +12209,7 @@
         <v>8</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>99.38</v>
+        <v>107.37</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>8</v>
@@ -12211,10 +12220,10 @@
         <v>2020</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>631</v>
@@ -12232,7 +12241,7 @@
         <v>8</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>99.18</v>
+        <v>106.61</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>8</v>
@@ -12264,7 +12273,7 @@
         <v>8</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>98.43</v>
+        <v>106.31</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>8</v>
@@ -12275,16 +12284,16 @@
         <v>2020</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>544</v>
+        <v>493</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>635</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>498</v>
+        <v>636</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>496</v>
@@ -12296,7 +12305,7 @@
         <v>8</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>97.71</v>
+        <v>105.26</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>8</v>
@@ -12307,16 +12316,16 @@
         <v>2020</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>637</v>
+        <v>498</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>496</v>
@@ -12328,7 +12337,7 @@
         <v>8</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>97.23</v>
+        <v>104.74</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>8</v>
@@ -12360,7 +12369,7 @@
         <v>8</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>94.55</v>
+        <v>102.63</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>8</v>
@@ -12392,7 +12401,7 @@
         <v>8</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>94.3</v>
+        <v>101.23</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>8</v>
@@ -12424,7 +12433,7 @@
         <v>8</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>92.87</v>
+        <v>99.96</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>8</v>
@@ -12435,10 +12444,10 @@
         <v>2020</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>644</v>
@@ -12456,7 +12465,7 @@
         <v>8</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>92.16</v>
+        <v>98.79</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>8</v>
@@ -12467,10 +12476,10 @@
         <v>2020</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>646</v>
@@ -12488,7 +12497,7 @@
         <v>8</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>91.9</v>
+        <v>98.59</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>8</v>
@@ -12499,10 +12508,10 @@
         <v>2020</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>648</v>
@@ -12520,7 +12529,7 @@
         <v>8</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>91.6</v>
+        <v>98.38</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>8</v>
@@ -12531,10 +12540,10 @@
         <v>2020</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>650</v>
@@ -12552,7 +12561,7 @@
         <v>8</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>91.28</v>
+        <v>98.25</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>8</v>
@@ -12584,7 +12593,7 @@
         <v>8</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>91.11</v>
+        <v>98.04</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>8</v>
@@ -12616,7 +12625,7 @@
         <v>8</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>90.32</v>
+        <v>97.97</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>8</v>
@@ -12648,7 +12657,7 @@
         <v>8</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>89.17</v>
+        <v>96.27</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>8</v>
@@ -12680,7 +12689,7 @@
         <v>8</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>87.28</v>
+        <v>93.93</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>8</v>
@@ -12712,7 +12721,7 @@
         <v>8</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>86.79</v>
+        <v>93.33</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>8</v>
@@ -12744,7 +12753,7 @@
         <v>8</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>85.62</v>
+        <v>92.66</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>8</v>
@@ -12776,7 +12785,7 @@
         <v>8</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>85.45</v>
+        <v>91.52</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>8</v>
@@ -12808,7 +12817,7 @@
         <v>8</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>84.84</v>
+        <v>91.41</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>8</v>
@@ -12840,7 +12849,7 @@
         <v>8</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>84.15</v>
+        <v>90.53</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>8</v>
@@ -12851,10 +12860,10 @@
         <v>2020</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>670</v>
@@ -12872,7 +12881,7 @@
         <v>8</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>83.19</v>
+        <v>89.98</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>8</v>
@@ -12883,10 +12892,10 @@
         <v>2020</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>672</v>
@@ -12904,7 +12913,7 @@
         <v>8</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>82.95</v>
+        <v>89.13</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>8</v>
@@ -12936,7 +12945,7 @@
         <v>8</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>82.55</v>
+        <v>88.98</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>8</v>
@@ -12968,7 +12977,7 @@
         <v>8</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>82.4</v>
+        <v>88.96</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>8</v>
@@ -13000,7 +13009,7 @@
         <v>8</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>81.44</v>
+        <v>88.5</v>
       </c>
       <c r="J326" s="2" t="s">
         <v>8</v>
@@ -13032,7 +13041,7 @@
         <v>8</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>80.9</v>
+        <v>86.95</v>
       </c>
       <c r="J327" s="2" t="s">
         <v>8</v>
@@ -13064,7 +13073,7 @@
         <v>8</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>80.74</v>
+        <v>86.92</v>
       </c>
       <c r="J328" s="2" t="s">
         <v>8</v>
@@ -13096,7 +13105,7 @@
         <v>8</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>80.61</v>
+        <v>85.8</v>
       </c>
       <c r="J329" s="2" t="s">
         <v>8</v>
@@ -13107,10 +13116,10 @@
         <v>2020</v>
       </c>
       <c r="B330" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>498</v>
+        <v>546</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>686</v>
@@ -13128,7 +13137,7 @@
         <v>8</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>77.68</v>
+        <v>83.34</v>
       </c>
       <c r="J330" s="2" t="s">
         <v>8</v>
@@ -13139,10 +13148,10 @@
         <v>2020</v>
       </c>
       <c r="B331" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>544</v>
+        <v>498</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>688</v>
@@ -13160,7 +13169,7 @@
         <v>8</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>77.37</v>
+        <v>83.27</v>
       </c>
       <c r="J331" s="2" t="s">
         <v>8</v>
@@ -13192,7 +13201,7 @@
         <v>8</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>76.88</v>
+        <v>83.03</v>
       </c>
       <c r="J332" s="2" t="s">
         <v>8</v>
@@ -13224,7 +13233,7 @@
         <v>8</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>76.8</v>
+        <v>82.33</v>
       </c>
       <c r="J333" s="2" t="s">
         <v>8</v>
@@ -13256,7 +13265,7 @@
         <v>8</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>76.19</v>
+        <v>81.81</v>
       </c>
       <c r="J334" s="2" t="s">
         <v>8</v>
@@ -13288,7 +13297,7 @@
         <v>8</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>74.45</v>
+        <v>80.43</v>
       </c>
       <c r="J335" s="2" t="s">
         <v>8</v>
@@ -13320,7 +13329,7 @@
         <v>8</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>73.83</v>
+        <v>79.55</v>
       </c>
       <c r="J336" s="2" t="s">
         <v>8</v>
@@ -13352,7 +13361,7 @@
         <v>8</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>73.13</v>
+        <v>78.28</v>
       </c>
       <c r="J337" s="2" t="s">
         <v>8</v>
@@ -13384,7 +13393,7 @@
         <v>8</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>69.04</v>
+        <v>74.12</v>
       </c>
       <c r="J338" s="2" t="s">
         <v>8</v>
@@ -13416,7 +13425,7 @@
         <v>8</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>65.73</v>
+        <v>70.66</v>
       </c>
       <c r="J339" s="2" t="s">
         <v>8</v>
@@ -13448,7 +13457,7 @@
         <v>8</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>61.34</v>
+        <v>66.07</v>
       </c>
       <c r="J340" s="2" t="s">
         <v>8</v>
@@ -13480,7 +13489,7 @@
         <v>8</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>54.44</v>
+        <v>58.22</v>
       </c>
       <c r="J341" s="2" t="s">
         <v>8</v>
@@ -13512,7 +13521,7 @@
         <v>8</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>46.47</v>
+        <v>50.42</v>
       </c>
       <c r="J342" s="2" t="s">
         <v>8</v>
@@ -13571,23 +13580,23 @@
         <v>719</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -13609,21 +13618,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
@@ -13632,7 +13641,7 @@
         <v>2020</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:41</t>
+    <t xml:space="preserve">2026-09-07 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2020.xlsx
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:41</t>
+    <t xml:space="preserve">2026-09-08 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
